--- a/doc/Journal de travail_Mini wheelie.xlsx
+++ b/doc/Journal de travail_Mini wheelie.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ABR\PRJ_2601_miniWheelie\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB39301D-4654-45EA-BA38-5E6A5BF1A92B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE58822-9C1D-47BE-B73E-BF536B0F0A29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3285" yWindow="1425" windowWidth="23610" windowHeight="11850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Test des valeurs PID (robot moyennement stable)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">correction de bugs </t>
+  </si>
+  <si>
+    <t>Ajustement du PID</t>
+  </si>
+  <si>
+    <t>modification de la calibration des moteur</t>
   </si>
 </sst>
 </file>
@@ -580,7 +589,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5703125" style="12"/>
@@ -767,7 +776,9 @@
       <c r="A15" s="10">
         <v>46148</v>
       </c>
-      <c r="B15" s="17"/>
+      <c r="B15" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="C15" s="14" t="s">
         <v>3</v>
       </c>
@@ -777,15 +788,35 @@
       <c r="A16" s="10">
         <v>46155</v>
       </c>
-      <c r="B16" s="17"/>
+      <c r="B16" s="17" t="s">
+        <v>21</v>
+      </c>
       <c r="C16" s="18"/>
       <c r="D16" s="19"/>
     </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="5"/>
+    <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
+        <v>46162</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+    </row>
+    <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>46169</v>
+      </c>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="11"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/Journal de travail_Mini wheelie.xlsx
+++ b/doc/Journal de travail_Mini wheelie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ABR\PRJ_2601_miniWheelie\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE58822-9C1D-47BE-B73E-BF536B0F0A29}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2340D06C-D28A-44EB-9392-83CC75214716}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="1425" windowWidth="23610" windowHeight="11850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26085" yWindow="885" windowWidth="23610" windowHeight="11850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Création dun journal de travail" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>Date</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Statut</t>
-  </si>
-  <si>
-    <t>En cours</t>
   </si>
   <si>
     <t>Terminé</t>
@@ -330,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -360,16 +357,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -609,7 +600,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -617,10 +608,10 @@
         <v>46050</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" s="7"/>
     </row>
@@ -629,13 +620,13 @@
         <v>46057</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -643,10 +634,10 @@
         <v>46064</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -655,13 +646,13 @@
         <v>46078</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
@@ -669,10 +660,10 @@
         <v>46085</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3"/>
     </row>
@@ -681,141 +672,147 @@
         <v>46092</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>46099</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="16">
-        <v>46099</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D8" s="17"/>
     </row>
     <row r="9" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="16">
+      <c r="A9" s="15">
         <v>46106</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D9" s="17"/>
     </row>
     <row r="10" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>46113</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>17</v>
+      <c r="B10" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>46120</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>18</v>
+      <c r="B11" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D11" s="17"/>
     </row>
     <row r="12" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>46127</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>16</v>
+      <c r="B12" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D12" s="17"/>
     </row>
     <row r="13" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="16">
+      <c r="A13" s="15">
         <v>46134</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>15</v>
+      <c r="B13" s="16" t="s">
+        <v>14</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D13" s="17"/>
     </row>
     <row r="14" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>46141</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>20</v>
+      <c r="B14" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>46148</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>22</v>
+      <c r="B15" s="16" t="s">
+        <v>21</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="17"/>
     </row>
     <row r="16" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="10">
         <v>46155</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
+      <c r="B16" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
         <v>46162</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
+      <c r="B17" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="17"/>
     </row>
     <row r="18" spans="1:4" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
         <v>46169</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="17"/>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="4"/>
-      <c r="C19" s="15"/>
+      <c r="C19" s="14"/>
       <c r="D19" s="5"/>
     </row>
   </sheetData>
